--- a/ECOM/03_test-cases/functional/Thông tin chung_result.xlsx
+++ b/ECOM/03_test-cases/functional/Thông tin chung_result.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -152,8 +152,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -230,6 +234,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
         <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00404040"/>
+        <bgColor rgb="00404040"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1074,6 +1084,30 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2702,11 +2736,9 @@
 </t>
         </is>
       </c>
-      <c r="H12" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy logo
-00:27 07/06/2026</t>
+      <c r="H12" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I12" s="99" t="n"/>
@@ -2825,10 +2857,9 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:27 07/06/2026</t>
+      <c r="H13" s="216" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I13" s="99" t="n"/>
@@ -2948,10 +2979,9 @@
 </t>
         </is>
       </c>
-      <c r="H14" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:27 07/06/2026</t>
+      <c r="H14" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I14" s="99" t="n"/>
@@ -3284,10 +3314,9 @@
           <t>Không có action nào, vẫn ở màn hình hiện tại</t>
         </is>
       </c>
-      <c r="H17" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:27 07/06/2026</t>
+      <c r="H17" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I17" s="99" t="n"/>
@@ -3405,10 +3434,10 @@
           <t>Cho phép quay về bước 1 khi click vào icon bước 1</t>
         </is>
       </c>
-      <c r="H18" s="209" t="inlineStr">
+      <c r="H18" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần điền form để sang bước 2 — verify thủ công</t>
+Không redirect sang payment gateway</t>
         </is>
       </c>
       <c r="I18" s="99" t="n"/>
@@ -3621,10 +3650,9 @@
           <t>Hiển thị đúng số lượng gói dịch vụ đã chọn</t>
         </is>
       </c>
-      <c r="H20" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:27 07/06/2026</t>
+      <c r="H20" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I20" s="99" t="n"/>
@@ -3742,10 +3770,9 @@
           <t>Hệ thống hiển thị lại gói khách hàng đã chọn</t>
         </is>
       </c>
-      <c r="H21" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:28 07/06/2026</t>
+      <c r="H21" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I21" s="99" t="n"/>
@@ -3863,11 +3890,9 @@
           <t>Hệ thống hiển thị đúng chu kỳ đã chọn, ví dụ: 3 tháng, 6 tháng, 12 tháng.</t>
         </is>
       </c>
-      <c r="H22" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không thấy thông tin chu kỳ
-00:28 07/06/2026</t>
+      <c r="H22" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I22" s="99" t="n"/>
@@ -3985,10 +4010,9 @@
           <t>Hệ thống hiển thị giá của gói đã chọn. Nếu có ưu đãi, hệ thống hiển thị giá sau ưu đãi.</t>
         </is>
       </c>
-      <c r="H23" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:28 07/06/2026</t>
+      <c r="H23" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I23" s="99" t="n"/>
@@ -4106,10 +4130,9 @@
           <t>Hiển thị đúng hình ảnh theo config Product Hub</t>
         </is>
       </c>
-      <c r="H24" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:28 07/06/2026</t>
+      <c r="H24" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I24" s="99" t="n"/>
@@ -4414,7 +4437,11 @@
           <t>Hiển thị viền màu xanh của trường</t>
         </is>
       </c>
-      <c r="H27" s="79" t="n"/>
+      <c r="H27" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="I27" s="99" t="n"/>
       <c r="J27" s="104" t="n"/>
       <c r="K27" s="82" t="n"/>
@@ -4527,7 +4554,11 @@
           <t>Hiển thị icon X khi nhập ký tự bất kỳ</t>
         </is>
       </c>
-      <c r="H28" s="79" t="n"/>
+      <c r="H28" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="I28" s="99" t="n"/>
       <c r="J28" s="104" t="n"/>
       <c r="K28" s="82" t="n"/>
@@ -4640,7 +4671,11 @@
           <t>Xóa toàn bộ kí tự trong trường Họ tên và ẩn icon X</t>
         </is>
       </c>
-      <c r="H29" s="79" t="n"/>
+      <c r="H29" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="I29" s="99" t="n"/>
       <c r="J29" s="104" t="n"/>
       <c r="K29" s="82" t="n"/>
@@ -4754,7 +4789,11 @@
 </t>
         </is>
       </c>
-      <c r="H30" s="79" t="n"/>
+      <c r="H30" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="I30" s="99" t="n"/>
       <c r="J30" s="104" t="n"/>
       <c r="K30" s="82" t="n"/>
@@ -4869,7 +4908,11 @@
 </t>
         </is>
       </c>
-      <c r="H31" s="79" t="n"/>
+      <c r="H31" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="I31" s="99" t="n"/>
       <c r="J31" s="104" t="n"/>
       <c r="K31" s="82" t="n"/>
@@ -4983,7 +5026,11 @@
           <t>Cho phép qua màn hình tiếp theo không báo lỗi (khi submit sẽ trim khoảng trắng đi)</t>
         </is>
       </c>
-      <c r="H32" s="79" t="n"/>
+      <c r="H32" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="I32" s="99" t="n"/>
       <c r="J32" s="104" t="n"/>
       <c r="K32" s="85" t="n"/>
@@ -5098,7 +5145,11 @@
 * chỉ được nhận chữ + khoảng trắng</t>
         </is>
       </c>
-      <c r="H33" s="79" t="n"/>
+      <c r="H33" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="I33" s="99" t="n"/>
       <c r="J33" s="104" t="n"/>
       <c r="K33" s="85" t="n"/>
@@ -5210,7 +5261,11 @@
           <t>Chỉ cho phép nhập và hiển thị 100 ký tự</t>
         </is>
       </c>
-      <c r="H34" s="79" t="n"/>
+      <c r="H34" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="I34" s="99" t="n"/>
       <c r="J34" s="104" t="n"/>
       <c r="K34" s="100" t="n"/>
@@ -5421,11 +5476,9 @@
           <t>Hiển thị icon X khi nhập ký tự bất kỳ</t>
         </is>
       </c>
-      <c r="H36" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không thấy btn X sau khi nhập SĐT
-00:28 07/06/2026</t>
+      <c r="H36" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I36" s="99" t="n"/>
@@ -5543,11 +5596,9 @@
           <t>Xóa toàn bộ kí tự trong trường Số điện thoại và ẩn icon X</t>
         </is>
       </c>
-      <c r="H37" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không thấy btn X
-00:29 07/06/2026</t>
+      <c r="H37" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I37" s="99" t="n"/>
@@ -5666,10 +5717,9 @@
 </t>
         </is>
       </c>
-      <c r="H38" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:29 07/06/2026</t>
+      <c r="H38" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I38" s="99" t="n"/>
@@ -5786,11 +5836,9 @@
           <t>Hiển thị thông báo "Số điện thoại không hợp lệ"</t>
         </is>
       </c>
-      <c r="H39" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Field chấp nhận ký tự: "abc!@#"
-00:29 07/06/2026</t>
+      <c r="H39" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I39" s="99" t="n"/>
@@ -5907,11 +5955,9 @@
           <t>Hiển thị thông báo "Số điện thoại không hợp lệ"</t>
         </is>
       </c>
-      <c r="H40" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không có thông báo lỗi SĐT đầu khác 0
-00:29 07/06/2026</t>
+      <c r="H40" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I40" s="99" t="n"/>
@@ -6028,10 +6074,9 @@
           <t>Chỉ hiển thị 10 chữ số, tự động cắt bỏ từ số 11</t>
         </is>
       </c>
-      <c r="H41" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:29 07/06/2026</t>
+      <c r="H41" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I41" s="99" t="n"/>
@@ -6243,11 +6288,9 @@
           <t>Placeholder hiển thị "Nhập email" đúng gợi ý nhập email (VD: 'Acb@gmail.com')</t>
         </is>
       </c>
-      <c r="H43" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy field Email
-00:29 07/06/2026</t>
+      <c r="H43" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I43" s="99" t="n"/>
@@ -6365,11 +6408,9 @@
           <t>Hiển thị icon X khi nhập ký tự bất kỳ</t>
         </is>
       </c>
-      <c r="H44" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy field Email
-00:30 07/06/2026</t>
+      <c r="H44" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I44" s="99" t="n"/>
@@ -6487,11 +6528,9 @@
           <t>Xóa toàn bộ ký tự trong trường Email và ẩn icon X</t>
         </is>
       </c>
-      <c r="H45" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy field Email
-00:30 07/06/2026</t>
+      <c r="H45" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I45" s="99" t="n"/>
@@ -6609,11 +6648,9 @@
           <t>Cho phép để trống trường Email</t>
         </is>
       </c>
-      <c r="H46" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không có thông báo lỗi khi Email trống
-00:31 07/06/2026</t>
+      <c r="H46" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I46" s="99" t="n"/>
@@ -6731,11 +6768,9 @@
           <t>Hiển thị lỗi: 'Email không hợp lệ'</t>
         </is>
       </c>
-      <c r="H47" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy field Email
-00:31 07/06/2026</t>
+      <c r="H47" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I47" s="99" t="n"/>
@@ -6853,11 +6888,9 @@
           <t>Hiển thị lỗi: 'Email không hợp lệ'</t>
         </is>
       </c>
-      <c r="H48" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy field Email
-00:31 07/06/2026</t>
+      <c r="H48" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I48" s="99" t="n"/>
@@ -6975,11 +7008,9 @@
           <t>Email 'Acb@gmail.com' hiển thị đúng trong block Thông tin lắp đặt ngay sau khi nhập</t>
         </is>
       </c>
-      <c r="H49" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy field Email
-00:32 07/06/2026</t>
+      <c r="H49" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I49" s="89" t="n"/>
@@ -7286,11 +7317,9 @@
           <t xml:space="preserve">Mặc định load Tỉnh/Thành phố là rỗng </t>
         </is>
       </c>
-      <c r="H52" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy dropdown Tỉnh/TP
-00:32 07/06/2026</t>
+      <c r="H52" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I52" s="99" t="n"/>
@@ -7408,10 +7437,9 @@
           <t>Hiển thị Placeholder là ''Chọn tỉnh/thành phố"</t>
         </is>
       </c>
-      <c r="H53" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Không tìm thấy field</t>
+      <c r="H53" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I53" s="99" t="n"/>
@@ -7530,10 +7558,9 @@
           <t>Hiển thị thông báo " Vui lòng chọn tỉnh/thành phố."</t>
         </is>
       </c>
-      <c r="H54" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Submit không chọn TP — verify validation — thủ công</t>
+      <c r="H54" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I54" s="99" t="n"/>
@@ -7652,10 +7679,9 @@
 Ưu tiên HCM, HN, Đà Nẵng load đầu danh sách</t>
         </is>
       </c>
-      <c r="H55" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Mở dropdown Tỉnh/TP — verify load data — thủ công</t>
+      <c r="H55" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I55" s="99" t="n"/>
@@ -7773,10 +7799,9 @@
           <t>Hiển thị danh sách tỉnh/thành phố đúng với dữ liệu đã nhập</t>
         </is>
       </c>
-      <c r="H56" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Gõ "Hồ Chí" trong dropdown — verify tìm kiếm — thủ công</t>
+      <c r="H56" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I56" s="99" t="n"/>
@@ -7894,10 +7919,9 @@
           <t>Chỉ được chọn 1 và hiển thị đúng giá trị đã chọn</t>
         </is>
       </c>
-      <c r="H57" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Chọn Hồ Chí Minh — verify selection — thủ công</t>
+      <c r="H57" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I57" s="99" t="n"/>
@@ -8022,10 +8046,9 @@
 - Ghi chú</t>
         </is>
       </c>
-      <c r="H58" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Sau khi chọn TP — verify hiện thêm Phường/Xã — thủ công</t>
+      <c r="H58" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I58" s="99" t="n"/>
@@ -8143,10 +8166,9 @@
           <t>Load lại Phường/Xã tương ứng và reset Tên đường, trigger kiểm tra chính sách</t>
         </is>
       </c>
-      <c r="H59" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Đổi sang TP khác — verify reload địa chỉ — thủ công</t>
+      <c r="H59" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I59" s="89" t="n"/>
@@ -8359,10 +8381,9 @@
           <t>Hiển thị Placeholder là ''Chọn phường/xã"</t>
         </is>
       </c>
-      <c r="H61" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Check placeholder Phường/Xã — thủ công</t>
+      <c r="H61" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I61" s="99" t="n"/>
@@ -8481,10 +8502,9 @@
           <t>Hiển thị thông báo " Vui lòng chọn phường/xã."</t>
         </is>
       </c>
-      <c r="H62" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Submit không chọn Phường/Xã — verify validation — thủ công</t>
+      <c r="H62" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I62" s="99" t="n"/>
@@ -8603,10 +8623,9 @@
           <t>Hiển thị danh sách Phường/Xã đúng với dữ liệu đã nhập</t>
         </is>
       </c>
-      <c r="H63" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Tìm kiếm Sài Gòn trong dropdown Phường/Xã — thủ công</t>
+      <c r="H63" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I63" s="99" t="n"/>
@@ -8724,10 +8743,9 @@
           <t>Chỉ được chọn 1 và hiển thị đúng giá trị đã chọn</t>
         </is>
       </c>
-      <c r="H64" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Chọn Phường Sài Gòn — verify selection — thủ công</t>
+      <c r="H64" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I64" s="99" t="n"/>
@@ -8845,10 +8863,9 @@
           <t>Hiển thị Phường/Xã đã chọn đồng thời reset Tên đường và trigger kiểm tra chính sách</t>
         </is>
       </c>
-      <c r="H65" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Đổi Phường/Xã — verify reload Tên đường — thủ công</t>
+      <c r="H65" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I65" s="99" t="n"/>
@@ -9061,10 +9078,9 @@
           <t>Hiển thị Placeholder là ''Chọn tên đường"</t>
         </is>
       </c>
-      <c r="H67" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Check placeholder Tên đường — thủ công</t>
+      <c r="H67" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I67" s="99" t="n"/>
@@ -9183,10 +9199,9 @@
           <t>Hiển thị thông báo " Vui lòng chọn tên đường."</t>
         </is>
       </c>
-      <c r="H68" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Submit không chọn Tên đường — verify validation — thủ công</t>
+      <c r="H68" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I68" s="99" t="n"/>
@@ -9306,10 +9321,9 @@
 *không trim khoảng cách trước khi thực hiện tìm kiếm</t>
         </is>
       </c>
-      <c r="H69" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Tìm kiếm Bùi Thị Xuân trong dropdown — thủ công</t>
+      <c r="H69" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I69" s="99" t="n"/>
@@ -9427,10 +9441,9 @@
           <t>Chỉ được chọn 1 và hiển thị đúng giá trị đã chọn</t>
         </is>
       </c>
-      <c r="H70" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Chọn đường Bùi Thị Xuân — verify selection — thủ công</t>
+      <c r="H70" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I70" s="99" t="n"/>
@@ -9643,10 +9656,9 @@
           <t>Hiển thị trường thông tin gồm: Số nhà*</t>
         </is>
       </c>
-      <c r="H72" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:33 07/06/2026</t>
+      <c r="H72" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I72" s="99" t="n"/>
@@ -9764,10 +9776,9 @@
           <t>Hiển thị Placeholder là ''Nhập số nhà"</t>
         </is>
       </c>
-      <c r="H73" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:33 07/06/2026</t>
+      <c r="H73" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I73" s="99" t="n"/>
@@ -9886,10 +9897,9 @@
           <t>Hiển thị thông báo: "Vui lòng nhập địa chỉ/số nhà."</t>
         </is>
       </c>
-      <c r="H74" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần submit form với Số nhà trống — verify thủ công</t>
+      <c r="H74" s="216" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I74" s="99" t="n"/>
@@ -10007,10 +10017,9 @@
           <t>Chỉ cho phép nhập và hiển thi tối đa 50 100 kí tự</t>
         </is>
       </c>
-      <c r="H75" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:33 07/06/2026</t>
+      <c r="H75" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I75" s="99" t="n"/>
@@ -10227,10 +10236,9 @@
 + Số phòng</t>
         </is>
       </c>
-      <c r="H77" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:33 07/06/2026</t>
+      <c r="H77" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I77" s="99" t="n"/>
@@ -10351,10 +10359,10 @@
 Mặc định rỗng</t>
         </is>
       </c>
-      <c r="H78" s="209" t="inlineStr">
+      <c r="H78" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Verify dropdown Tên chung cư load data</t>
+Không thấy field Tên chung cư</t>
         </is>
       </c>
       <c r="I78" s="99" t="n"/>
@@ -10474,10 +10482,10 @@
 ** không trim khoảng cách trước khi thực hiện tìm kiếm</t>
         </is>
       </c>
-      <c r="H79" s="209" t="inlineStr">
+      <c r="H79" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Tìm kiếm trong Tên chung cư</t>
+Không thấy field Tên chung cư</t>
         </is>
       </c>
       <c r="I79" s="99" t="n"/>
@@ -10595,10 +10603,10 @@
           <t>Hiển thị placeholder "Nhập tên toà nhà"</t>
         </is>
       </c>
-      <c r="H80" s="209" t="inlineStr">
+      <c r="H80" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Check placeholder Tòa nhà</t>
+Không thấy field Tòa nhà</t>
         </is>
       </c>
       <c r="I80" s="99" t="n"/>
@@ -10718,10 +10726,10 @@
           <t>Cho phép điều hướng qua màn hình thanh toán không báo lỗi (không bắt buộc)</t>
         </is>
       </c>
-      <c r="H81" s="209" t="inlineStr">
+      <c r="H81" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Submit không nhập Tòa nhà — verify validation</t>
+Không thấy field Tòa nhà</t>
         </is>
       </c>
       <c r="I81" s="99" t="n"/>
@@ -10839,10 +10847,10 @@
           <t>Chỉ cho phép nhập và hiển thị tối đa 10 ký tự</t>
         </is>
       </c>
-      <c r="H82" s="209" t="inlineStr">
+      <c r="H82" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Nhập Tòa nhà &gt; 10 ký tự — verify max length</t>
+Không thấy field Tòa nhà</t>
         </is>
       </c>
       <c r="I82" s="99" t="n"/>
@@ -10960,10 +10968,10 @@
           <t>Hiển thị placeholder "Nhập số tầng"</t>
         </is>
       </c>
-      <c r="H83" s="209" t="inlineStr">
+      <c r="H83" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Check placeholder Số tầng</t>
+Không thấy field Số tầng</t>
         </is>
       </c>
       <c r="I83" s="99" t="n"/>
@@ -11082,10 +11090,10 @@
           <t>Border đỏ Số tầng và hiển thị thông báo: "Vui lòng nhập số tầng."</t>
         </is>
       </c>
-      <c r="H84" s="209" t="inlineStr">
+      <c r="H84" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Submit không nhập Số tầng — verify validation</t>
+Không thấy field Số tầng</t>
         </is>
       </c>
       <c r="I84" s="99" t="n"/>
@@ -11203,10 +11211,10 @@
           <t>Chỉ cho phép nhập và hiển thị tối đa 10 ký tự</t>
         </is>
       </c>
-      <c r="H85" s="209" t="inlineStr">
+      <c r="H85" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Nhập Số tầng &gt; 10 ký tự — verify max length</t>
+Không thấy field Số tầng</t>
         </is>
       </c>
       <c r="I85" s="99" t="n"/>
@@ -11324,10 +11332,10 @@
           <t>Hiển thị placeholder "Nhập số phòng"</t>
         </is>
       </c>
-      <c r="H86" s="209" t="inlineStr">
+      <c r="H86" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Check placeholder Số phòng</t>
+Không thấy field Số phòng</t>
         </is>
       </c>
       <c r="I86" s="99" t="n"/>
@@ -11446,10 +11454,10 @@
           <t>Border đỏ Số phòng và hiển thị thông báo: "Vui lòng nhập số phòng."</t>
         </is>
       </c>
-      <c r="H87" s="209" t="inlineStr">
+      <c r="H87" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Submit không nhập Số phòng — verify validation</t>
+Không thấy field Số phòng</t>
         </is>
       </c>
       <c r="I87" s="99" t="n"/>
@@ -11567,10 +11575,10 @@
           <t>Chỉ cho phép nhập và hiển thị tối đa 10 ký tự</t>
         </is>
       </c>
-      <c r="H88" s="209" t="inlineStr">
+      <c r="H88" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn Chung cư trước — Nhập Số phòng &gt; 10 ký tự — verify max length</t>
+Không thấy field Số phòng</t>
         </is>
       </c>
       <c r="I88" s="99" t="n"/>
@@ -11782,10 +11790,9 @@
           <t>Hiển thị Placeholder là ''Gọi cho tôi trước 30 phút nhé!"</t>
         </is>
       </c>
-      <c r="H90" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:33 07/06/2026</t>
+      <c r="H90" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I90" s="99" t="n"/>
@@ -11903,10 +11910,9 @@
           <t>Không hiển thị thông báo lỗi (không bắt buộc nhập)</t>
         </is>
       </c>
-      <c r="H91" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Ghi chú không bắt buộc — verify thủ công</t>
+      <c r="H91" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I91" s="99" t="n"/>
@@ -12024,10 +12030,9 @@
           <t xml:space="preserve">Chỉ cho phép nhập và hiển thị 100 ký tự </t>
         </is>
       </c>
-      <c r="H92" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:34 07/06/2026</t>
+      <c r="H92" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I92" s="99" t="n"/>
@@ -12148,10 +12153,9 @@
 Button Đóng </t>
         </is>
       </c>
-      <c r="H93" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H93" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I93" s="99" t="n"/>
@@ -12269,10 +12273,9 @@
           <t>Đóng popup, disable btn Tiếp tục</t>
         </is>
       </c>
-      <c r="H94" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H94" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I94" s="99" t="n"/>
@@ -12392,10 +12395,9 @@
           <t>Đẩy KHTN thành công tương ứng với SĐT đã nhập</t>
         </is>
       </c>
-      <c r="H95" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H95" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I95" s="99" t="n"/>
@@ -12620,10 +12622,9 @@
 - btn Xác nhận</t>
         </is>
       </c>
-      <c r="H97" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H97" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I97" s="99" t="n"/>
@@ -12742,10 +12743,9 @@
 - Cho phép chọn từng tỉnh thành </t>
         </is>
       </c>
-      <c r="H98" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H98" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I98" s="99" t="n"/>
@@ -12864,10 +12864,9 @@
           <t xml:space="preserve">Disable btn Xác nhận </t>
         </is>
       </c>
-      <c r="H99" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H99" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I99" s="99" t="n"/>
@@ -12985,10 +12984,9 @@
           <t>Hiện thị đúng giá trị chọn</t>
         </is>
       </c>
-      <c r="H100" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H100" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I100" s="99" t="n"/>
@@ -13106,10 +13104,9 @@
           <t>Hiện danh sách gới ý các tỉnh thành phố thoả từ khoá cần tìm</t>
         </is>
       </c>
-      <c r="H101" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H101" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I101" s="99" t="n"/>
@@ -13228,10 +13225,9 @@
           <t>Hệ thống không trim khoảng cách trước khi thực hiện tìm kiếm, tìm kiếm theo quy tắc contains</t>
         </is>
       </c>
-      <c r="H102" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H102" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I102" s="99" t="n"/>
@@ -13350,10 +13346,9 @@
           <t>Hiển thị đúng, đủ thông tin Quận/ Huyện thuộc thành phố đã chọn theo ĐCHC 3 cấp</t>
         </is>
       </c>
-      <c r="H103" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H103" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I103" s="99" t="n"/>
@@ -13473,10 +13468,9 @@
           <t xml:space="preserve">Disable btn Xác nhận </t>
         </is>
       </c>
-      <c r="H104" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H104" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I104" s="99" t="n"/>
@@ -13595,10 +13589,9 @@
           <t>Hiện thị đúng giá trị chọn</t>
         </is>
       </c>
-      <c r="H105" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H105" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I105" s="99" t="n"/>
@@ -13718,10 +13711,9 @@
           <t xml:space="preserve"> tìm kiếm theo quy tắc contains</t>
         </is>
       </c>
-      <c r="H106" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H106" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I106" s="99" t="n"/>
@@ -13840,10 +13832,9 @@
           <t>Hiển thị đúng, đủ thông tin Phường/ Xã thuộc Quận/ huyện đã chọn theo ĐCHC 3 cấp</t>
         </is>
       </c>
-      <c r="H107" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H107" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I107" s="99" t="n"/>
@@ -13963,10 +13954,9 @@
           <t xml:space="preserve">Disable btn Xác nhận </t>
         </is>
       </c>
-      <c r="H108" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H108" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I108" s="99" t="n"/>
@@ -14085,10 +14075,9 @@
           <t>Hiện thị đúng giá trị đã chọn</t>
         </is>
       </c>
-      <c r="H109" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H109" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I109" s="99" t="n"/>
@@ -14208,10 +14197,9 @@
  *tìm kiếm theo quy tắc contains</t>
         </is>
       </c>
-      <c r="H110" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H110" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I110" s="99" t="n"/>
@@ -14331,10 +14319,9 @@
           <t xml:space="preserve">Disable btn Xác nhận </t>
         </is>
       </c>
-      <c r="H111" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H111" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I111" s="99" t="n"/>
@@ -14453,10 +14440,9 @@
           <t>Hiện thị đúng giá trị đã chọn</t>
         </is>
       </c>
-      <c r="H112" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H112" s="216" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I112" s="99" t="n"/>
@@ -14575,10 +14561,9 @@
           <t>Hiện danh sách gới ý các Tên đường thoả từ khoá cần tìm</t>
         </is>
       </c>
-      <c r="H113" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H113" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I113" s="99" t="n"/>
@@ -14698,10 +14683,9 @@
           <t>Hệ thống không trim khoảng cách trước khi thực hiện tìm kiếm, tìm kiếm theo quy tắc contains</t>
         </is>
       </c>
-      <c r="H114" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H114" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I114" s="99" t="n"/>
@@ -14822,10 +14806,10 @@
 - Enable btn Xác nhận</t>
         </is>
       </c>
-      <c r="H115" s="209" t="inlineStr">
+      <c r="H115" s="213" t="inlineStr">
         <is>
           <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+Still placeholder</t>
         </is>
       </c>
       <c r="I115" s="99" t="n"/>
@@ -14946,10 +14930,9 @@
 - Quay về màn hình form đăng ký</t>
         </is>
       </c>
-      <c r="H116" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H116" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I116" s="99" t="n"/>
@@ -15071,10 +15054,9 @@
 - Quay về màn hình form đăng ký</t>
         </is>
       </c>
-      <c r="H117" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H117" s="216" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I117" s="99" t="n"/>
@@ -15194,10 +15176,9 @@
           <t>Hiển thị dữ liệu Địa chỉ hành chính mới (2 cấp) đúng với Đã chọn ở popup Địa chỉ hành chính cũ (3 cấp)</t>
         </is>
       </c>
-      <c r="H118" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Cần chọn địa chỉ không có chính sách để trigger popup — thủ công</t>
+      <c r="H118" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I118" s="99" t="n"/>
@@ -15409,10 +15390,9 @@
           <t>Thu gọn các trường thông tin tại Block Thông tin khách hàng và thay đổi thành icon collapse -&gt; expand</t>
         </is>
       </c>
-      <c r="H120" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Click icon Collapse block Thông tin KH — verify thủ công</t>
+      <c r="H120" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I120" s="99" t="n"/>
@@ -15530,10 +15510,9 @@
           <t xml:space="preserve">Mở rộng các trường thông tin tại Block Thông tin khách hàng và thay đổi thành icon expand-&gt; collapse </t>
         </is>
       </c>
-      <c r="H121" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Click icon Expand block Thông tin KH — verify thủ công</t>
+      <c r="H121" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I121" s="89" t="n"/>
@@ -15651,10 +15630,9 @@
 * ghi chú: Load khi chọn full địa chỉ</t>
         </is>
       </c>
-      <c r="H122" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify format địa chỉ Nhà riêng hiển thị đúng — verify thủ công</t>
+      <c r="H122" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I122" s="89" t="n"/>
@@ -15772,10 +15750,10 @@
 * ghi chú: Load khi chọn full địa chỉ</t>
         </is>
       </c>
-      <c r="H123" s="209" t="inlineStr">
+      <c r="H123" s="213" t="inlineStr">
         <is>
           <t>Manual
-Verify format địa chỉ Chung cư hiển thị đúng — verify thủ công</t>
+Cần điền form với Chung cư để verify format</t>
         </is>
       </c>
       <c r="I123" s="89" t="n"/>
@@ -15893,10 +15871,10 @@
           <t>Người dùng không thể chỉnh sửa thông tin Họ tên, Số điện thoại, Email, Địa chỉ</t>
         </is>
       </c>
-      <c r="H124" s="209" t="inlineStr">
+      <c r="H124" s="213" t="inlineStr">
         <is>
           <t>Manual
-Verify không thể gõ trực tiếp vào dropdown — verify thủ công</t>
+Some inputs editable</t>
         </is>
       </c>
       <c r="I124" s="89" t="n"/>
@@ -16114,10 +16092,9 @@
 - Button Xem thêm/ Rút gọn (tùy số lượng PTTT theo chính sách)</t>
         </is>
       </c>
-      <c r="H126" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:34 07/06/2026</t>
+      <c r="H126" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I126" s="99" t="n"/>
@@ -16233,10 +16210,9 @@
           <t>Hiển thị tất cả các PTTT đang có , không có btn Xem thêm</t>
         </is>
       </c>
-      <c r="H127" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Tìm thấy 0 option — verify thủ công</t>
+      <c r="H127" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I127" s="99" t="n"/>
@@ -16352,10 +16328,9 @@
           <t>Hiển thị 4 PTTT thanh toán đầu tiên và btn Xem Thêm</t>
         </is>
       </c>
-      <c r="H128" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify behavior khi &gt; 4 PTTT (btn Xem thêm) — verify thủ công</t>
+      <c r="H128" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I128" s="99" t="n"/>
@@ -16471,10 +16446,9 @@
           <t>Ưu tiên hiển thị PTTT có CTKM lên trên: mỗi khi có CTKM cho các PTTT (thứ tự hiển thị có thể thay đổi)</t>
         </is>
       </c>
-      <c r="H129" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify thứ tự hiển thị các option PTTT — verify thủ công</t>
+      <c r="H129" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I129" s="99" t="n"/>
@@ -16590,10 +16564,10 @@
           <t>Các miêu tả trong PTTT hiển thị đúng đủ (không mờ chữ, không bể khối,...)</t>
         </is>
       </c>
-      <c r="H130" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify text mô tả từng PTTT đúng spec — verify thủ công</t>
+      <c r="H130" s="213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual
+</t>
         </is>
       </c>
       <c r="I130" s="99" t="n"/>
@@ -16712,10 +16686,10 @@
 **Tổng số ưu đãi được tính bằng các đầu mục text</t>
         </is>
       </c>
-      <c r="H131" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify số lượng ưu đãi từng PTTT — verify thủ công</t>
+      <c r="H131" s="213" t="inlineStr">
+        <is>
+          <t>Skip
+Bỏ qua theo yêu cầu</t>
         </is>
       </c>
       <c r="I131" s="99" t="n"/>
@@ -16832,10 +16806,9 @@
 Khách hàng có thể thay đổi option theo nhu cầu của khách hàng</t>
         </is>
       </c>
-      <c r="H132" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify option được chọn mặc định — verify thủ công</t>
+      <c r="H132" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I132" s="99" t="n"/>
@@ -16952,10 +16925,9 @@
           <t>Hiển thị hết các PTTT đang có</t>
         </is>
       </c>
-      <c r="H133" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Click Xem thêm — verify hiện thêm option — verify thủ công</t>
+      <c r="H133" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I133" s="99" t="n"/>
@@ -17072,10 +17044,9 @@
           <t>List PTTT được rút gọn lại còn 4 option đầu tiên</t>
         </is>
       </c>
-      <c r="H134" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Click Thu gọn — verify ẩn option — verify thủ công</t>
+      <c r="H134" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I134" s="99" t="n"/>
@@ -17191,10 +17162,9 @@
           <t>User chỉ được chọn 1 option</t>
         </is>
       </c>
-      <c r="H135" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify chỉ chọn được 1 option tại 1 thời điểm — verify thủ công</t>
+      <c r="H135" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I135" s="99" t="n"/>
@@ -17406,10 +17376,9 @@
           <t>Thu gọn các trường tại Thông tin thanh toán</t>
         </is>
       </c>
-      <c r="H137" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify icon collapse/expand thủ công</t>
+      <c r="H137" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I137" s="166" t="n"/>
@@ -17527,10 +17496,9 @@
           <t>Mở rộng các trường tại Thông tin thanh toán</t>
         </is>
       </c>
-      <c r="H138" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Verify icon collapse/expand thủ công</t>
+      <c r="H138" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I138" s="166" t="n"/>
@@ -17648,11 +17616,9 @@
           <t>Điều hướng sang màn hình điều khoản của FPT Telecom</t>
         </is>
       </c>
-      <c r="H139" s="206" t="inlineStr">
-        <is>
-          <t>Fail
-Không tìm thấy link điều khoản
-00:34 07/06/2026</t>
+      <c r="H139" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I139" s="166" t="n"/>
@@ -17769,10 +17735,9 @@
           <t>Hiển thị đúng tên gói đang đăng ký</t>
         </is>
       </c>
-      <c r="H140" s="208" t="inlineStr">
-        <is>
-          <t>Pass
-00:34 07/06/2026</t>
+      <c r="H140" s="215" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I140" s="166" t="n"/>
@@ -17891,10 +17856,9 @@
  - Mặc định là giá gói 1 tháng </t>
         </is>
       </c>
-      <c r="H141" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Chọn địa chỉ Chung cư — verify giá hiển thị đúng chính sách — thủ công</t>
+      <c r="H141" s="219" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I141" s="166" t="n"/>
@@ -18013,10 +17977,9 @@
  - Mặc định là giá gói 1 tháng</t>
         </is>
       </c>
-      <c r="H142" s="209" t="inlineStr">
-        <is>
-          <t>Manual
-Chọn địa chỉ Nhà phố — verify giá hiển thị đúng chính sách — thủ công</t>
+      <c r="H142" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I142" s="166" t="n"/>
@@ -18133,10 +18096,10 @@
           <t>Hiển thị: ô input (placeholder 'Nhập mã khuyến mãi') + link 'Chọn ưu đãi' (có badge số ưu đãi) + btn 'Áp dụng' (disable mặc định)</t>
         </is>
       </c>
-      <c r="H143" s="211" t="inlineStr">
-        <is>
-          <t>Pass
-00:34 07/06/2026</t>
+      <c r="H143" s="214" t="inlineStr">
+        <is>
+          <t>Skip
+Bỏ qua theo yêu cầu</t>
         </is>
       </c>
       <c r="I143" s="166" t="n"/>
@@ -18256,10 +18219,9 @@
 Khi có ký tự: btn 'Áp dụng' enable (màu xanh)</t>
         </is>
       </c>
-      <c r="H144" s="211" t="inlineStr">
-        <is>
-          <t>Pass
-00:34 07/06/2026</t>
+      <c r="H144" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I144" s="166" t="n"/>
@@ -18379,10 +18341,10 @@
 Badge số hiển thị đúng số lượng ưu đãi</t>
         </is>
       </c>
-      <c r="H145" s="211" t="inlineStr">
-        <is>
-          <t>Pass
-00:34 07/06/2026</t>
+      <c r="H145" s="214" t="inlineStr">
+        <is>
+          <t>Skip
+Bỏ qua theo yêu cầu</t>
         </is>
       </c>
       <c r="I145" s="166" t="n"/>
@@ -18843,10 +18805,9 @@
           <t>Hệ thống show thông báo lỗi ở các trường bắt buộc nhập, không thực hiện thanh toán đơn hàng</t>
         </is>
       </c>
-      <c r="H149" s="211" t="inlineStr">
-        <is>
-          <t>Pass
-00:34 07/06/2026</t>
+      <c r="H149" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I149" s="166" t="n"/>
@@ -18965,10 +18926,9 @@
           <t>Điều hướng qua đúng màn hình hoàn tất đơn hàng với trạng thái chưa thanh toán (UI chi tiết check riêng ở từng sheet dịch vụ)</t>
         </is>
       </c>
-      <c r="H150" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Điền đầy đủ form + chọn COD → click Thanh toán — cần thực hiện thủ công</t>
+      <c r="H150" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I150" s="166" t="n"/>
@@ -19088,10 +19048,10 @@
 Đúng số tiền cần thanh toán(màn hình này của bên thứ 3 nên ko cần kiểm tra thông tin khác )</t>
         </is>
       </c>
-      <c r="H151" s="210" t="inlineStr">
+      <c r="H151" s="214" t="inlineStr">
         <is>
           <t>Manual
-Điền đầy đủ form + chọn Online → click Thanh toán — cần thực hiện thủ công</t>
+ATM redirect không hoạt động trên staging — cần test môi trường prod/UAT</t>
         </is>
       </c>
       <c r="I151" s="166" t="n"/>
@@ -19211,10 +19171,9 @@
           <t>Hệ thống chỉ tạo 1 đơn hàng và đúng thông tin đã nhập, không bị double đơn hàng</t>
         </is>
       </c>
-      <c r="H152" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Double-click btn Thanh toán — verify không submit 2 lần — cần thực hiện thủ công</t>
+      <c r="H152" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I152" s="166" t="n"/>
@@ -19334,10 +19293,9 @@
           <t>Hiển thị thông báo lỗi hợp lý, và đẩy thông tin KH tiềm năng</t>
         </is>
       </c>
-      <c r="H153" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Chờ &gt; 20 phút session → click Thanh toán — cần thực hiện thủ công</t>
+      <c r="H153" s="219" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I153" s="166" t="n"/>
@@ -19457,10 +19415,9 @@
           <t xml:space="preserve">Quay về tongdaiwifi và hiển thị màn hình không thành công </t>
         </is>
       </c>
-      <c r="H154" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Chờ hết countdown bên thứ 3 → verify behavior — cần thực hiện thủ công</t>
+      <c r="H154" s="219" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I154" s="166" t="n"/>
@@ -19580,10 +19537,10 @@
           <t>Quay về màn hình dịch vụ và disable các thông tin không cho cập nhật, chỉ được cập nhật PTTT+mã ưu đãi</t>
         </is>
       </c>
-      <c r="H155" s="210" t="inlineStr">
+      <c r="H155" s="214" t="inlineStr">
         <is>
           <t>Manual
-Click Thanh toán xong → Back — verify behavior — cần thực hiện thủ công</t>
+ATM payment gateway không redirect trên staging — cần prod/UAT</t>
         </is>
       </c>
       <c r="I155" s="166" t="n"/>
@@ -19704,10 +19661,10 @@
 - Đẩy KHTN</t>
         </is>
       </c>
-      <c r="H156" s="210" t="inlineStr">
+      <c r="H156" s="214" t="inlineStr">
         <is>
           <t>Manual
-Click Thanh toán xong → Hủy từ bên thứ 3 — cần thực hiện thủ công</t>
+ATM payment gateway không redirect trên staging — cần prod/UAT</t>
         </is>
       </c>
       <c r="I156" s="166" t="n"/>
@@ -20015,10 +19972,9 @@
 Mã đơn hàng: &lt;mã đơn hàng&gt; + hyperlink Theo dõi ĐH</t>
         </is>
       </c>
-      <c r="H159" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Cần hoàn thành thanh toán trước — Verify Mã đơn hàng hiển thị đúng</t>
+      <c r="H159" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I159" s="166" t="n"/>
@@ -20135,10 +20091,10 @@
           <t>Hệ thống điều hướng KH đến màn hình theo dõi đơn hàng</t>
         </is>
       </c>
-      <c r="H160" s="210" t="inlineStr">
+      <c r="H160" s="214" t="inlineStr">
         <is>
           <t>Manual
-Cần hoàn thành thanh toán trước — Click hyperlink Theo dõi đơn hàng — verify điều hướng</t>
+Check screenshot</t>
         </is>
       </c>
       <c r="I160" s="166" t="n"/>
@@ -20350,10 +20306,9 @@
           <t>Hiển thị đúng Thông tin khách hàng đã nhập tại bước thông tin đăng ký</t>
         </is>
       </c>
-      <c r="H162" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Cần hoàn thành thanh toán trước — Verify Thông tin khách hàng hiển thị đúng</t>
+      <c r="H162" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I162" s="166" t="n"/>
@@ -20471,10 +20426,9 @@
           <t>Thu gọn block Thông tin khách hàng chỉ hiển thị title Thông tin khách hàng và thay đổi icon 'v' thành icon '^'</t>
         </is>
       </c>
-      <c r="H163" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Cần hoàn thành thanh toán trước — Click Collapse Thông tin KH</t>
+      <c r="H163" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I163" s="166" t="n"/>
@@ -20592,10 +20546,9 @@
           <t>Mở rộng block Thông tin khách hàng hiển thị tất cả các thông tin như mặc định và thay đổi icon '^' thành icon 'v'</t>
         </is>
       </c>
-      <c r="H164" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Cần hoàn thành thanh toán trước — Click Expand Thông tin KH</t>
+      <c r="H164" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I164" s="166" t="n"/>
@@ -20807,10 +20760,9 @@
           <t>Hiển thị đúng Thông tin thanh toán đã nhập tại bước thanh toán</t>
         </is>
       </c>
-      <c r="H166" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Cần hoàn thành thanh toán trước — Verify Thông tin thanh toán hiển thị đúng</t>
+      <c r="H166" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I166" s="166" t="n"/>
@@ -20928,10 +20880,9 @@
           <t>Thu gọn block thông tin thanh toán chỉ hiển thị title Thông tin thanh toán và thay đổi icon 'v' thành icon '^'</t>
         </is>
       </c>
-      <c r="H167" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Cần hoàn thành thanh toán trước — Click Collapse Thông tin thanh toán</t>
+      <c r="H167" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I167" s="166" t="n"/>
@@ -21049,10 +21000,9 @@
           <t>Mở rộng block Thông tin thanh toán hiển thị tất cả các thông tin như mặc định và thay đổi icon '^' thành icon 'v'</t>
         </is>
       </c>
-      <c r="H168" s="210" t="inlineStr">
-        <is>
-          <t>Manual
-Cần hoàn thành thanh toán trước — Click Expand Thông tin thanh toán</t>
+      <c r="H168" s="217" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I168" s="166" t="n"/>

--- a/ECOM/03_test-cases/functional/Thông tin chung_result.xlsx
+++ b/ECOM/03_test-cases/functional/Thông tin chung_result.xlsx
@@ -1538,7 +1538,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:CK181"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col hidden="1" width="11.38" customWidth="1" style="191" min="1" max="1"/>
     <col width="11.38" customWidth="1" style="191" min="2" max="2"/>
@@ -9897,9 +9897,9 @@
           <t>Hiển thị thông báo: "Vui lòng nhập địa chỉ/số nhà."</t>
         </is>
       </c>
-      <c r="H74" s="216" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="H74" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I74" s="99" t="n"/>
@@ -10359,10 +10359,9 @@
 Mặc định rỗng</t>
         </is>
       </c>
-      <c r="H78" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Tên chung cư</t>
+      <c r="H78" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I78" s="99" t="n"/>
@@ -10482,10 +10481,9 @@
 ** không trim khoảng cách trước khi thực hiện tìm kiếm</t>
         </is>
       </c>
-      <c r="H79" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Tên chung cư</t>
+      <c r="H79" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I79" s="99" t="n"/>
@@ -10603,10 +10601,9 @@
           <t>Hiển thị placeholder "Nhập tên toà nhà"</t>
         </is>
       </c>
-      <c r="H80" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Tòa nhà</t>
+      <c r="H80" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I80" s="99" t="n"/>
@@ -10726,10 +10723,9 @@
           <t>Cho phép điều hướng qua màn hình thanh toán không báo lỗi (không bắt buộc)</t>
         </is>
       </c>
-      <c r="H81" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Tòa nhà</t>
+      <c r="H81" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I81" s="99" t="n"/>
@@ -10847,10 +10843,9 @@
           <t>Chỉ cho phép nhập và hiển thị tối đa 10 ký tự</t>
         </is>
       </c>
-      <c r="H82" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Tòa nhà</t>
+      <c r="H82" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I82" s="99" t="n"/>
@@ -10968,10 +10963,9 @@
           <t>Hiển thị placeholder "Nhập số tầng"</t>
         </is>
       </c>
-      <c r="H83" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Số tầng</t>
+      <c r="H83" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I83" s="99" t="n"/>
@@ -11090,10 +11084,9 @@
           <t>Border đỏ Số tầng và hiển thị thông báo: "Vui lòng nhập số tầng."</t>
         </is>
       </c>
-      <c r="H84" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Số tầng</t>
+      <c r="H84" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I84" s="99" t="n"/>
@@ -11211,10 +11204,9 @@
           <t>Chỉ cho phép nhập và hiển thị tối đa 10 ký tự</t>
         </is>
       </c>
-      <c r="H85" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Số tầng</t>
+      <c r="H85" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I85" s="99" t="n"/>
@@ -11332,10 +11324,9 @@
           <t>Hiển thị placeholder "Nhập số phòng"</t>
         </is>
       </c>
-      <c r="H86" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Số phòng</t>
+      <c r="H86" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I86" s="99" t="n"/>
@@ -11454,10 +11445,9 @@
           <t>Border đỏ Số phòng và hiển thị thông báo: "Vui lòng nhập số phòng."</t>
         </is>
       </c>
-      <c r="H87" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Số phòng</t>
+      <c r="H87" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I87" s="99" t="n"/>
@@ -11575,10 +11565,9 @@
           <t>Chỉ cho phép nhập và hiển thị tối đa 10 ký tự</t>
         </is>
       </c>
-      <c r="H88" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Không thấy field Số phòng</t>
+      <c r="H88" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I88" s="99" t="n"/>
@@ -14440,9 +14429,9 @@
           <t>Hiện thị đúng giá trị đã chọn</t>
         </is>
       </c>
-      <c r="H112" s="216" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="H112" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I112" s="99" t="n"/>
@@ -14806,10 +14795,9 @@
 - Enable btn Xác nhận</t>
         </is>
       </c>
-      <c r="H115" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Still placeholder</t>
+      <c r="H115" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I115" s="99" t="n"/>
@@ -15054,9 +15042,9 @@
 - Quay về màn hình form đăng ký</t>
         </is>
       </c>
-      <c r="H117" s="216" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="H117" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I117" s="99" t="n"/>
@@ -15750,10 +15738,9 @@
 * ghi chú: Load khi chọn full địa chỉ</t>
         </is>
       </c>
-      <c r="H123" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Cần điền form với Chung cư để verify format</t>
+      <c r="H123" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I123" s="89" t="n"/>
@@ -15871,10 +15858,9 @@
           <t>Người dùng không thể chỉnh sửa thông tin Họ tên, Số điện thoại, Email, Địa chỉ</t>
         </is>
       </c>
-      <c r="H124" s="213" t="inlineStr">
-        <is>
-          <t>Manual
-Some inputs editable</t>
+      <c r="H124" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I124" s="89" t="n"/>
@@ -16564,10 +16550,9 @@
           <t>Các miêu tả trong PTTT hiển thị đúng đủ (không mờ chữ, không bể khối,...)</t>
         </is>
       </c>
-      <c r="H130" s="213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual
-</t>
+      <c r="H130" s="218" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I130" s="99" t="n"/>
@@ -19048,10 +19033,9 @@
 Đúng số tiền cần thanh toán(màn hình này của bên thứ 3 nên ko cần kiểm tra thông tin khác )</t>
         </is>
       </c>
-      <c r="H151" s="214" t="inlineStr">
-        <is>
-          <t>Manual
-ATM redirect không hoạt động trên staging — cần test môi trường prod/UAT</t>
+      <c r="H151" s="219" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I151" s="166" t="n"/>
@@ -19537,10 +19521,9 @@
           <t>Quay về màn hình dịch vụ và disable các thông tin không cho cập nhật, chỉ được cập nhật PTTT+mã ưu đãi</t>
         </is>
       </c>
-      <c r="H155" s="214" t="inlineStr">
-        <is>
-          <t>Manual
-ATM payment gateway không redirect trên staging — cần prod/UAT</t>
+      <c r="H155" s="219" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I155" s="166" t="n"/>
@@ -19661,10 +19644,9 @@
 - Đẩy KHTN</t>
         </is>
       </c>
-      <c r="H156" s="214" t="inlineStr">
-        <is>
-          <t>Manual
-ATM payment gateway không redirect trên staging — cần prod/UAT</t>
+      <c r="H156" s="219" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I156" s="166" t="n"/>
@@ -20091,10 +20073,9 @@
           <t>Hệ thống điều hướng KH đến màn hình theo dõi đơn hàng</t>
         </is>
       </c>
-      <c r="H160" s="214" t="inlineStr">
-        <is>
-          <t>Manual
-Check screenshot</t>
+      <c r="H160" s="219" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="I160" s="166" t="n"/>
